--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a1.00_b1.00_x0.30_Q20_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a1.00_b1.00_x0.30_Q20_LO.xlsx
@@ -455,10 +455,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03160859091247534</v>
+        <v>0.01671303745747379</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03160859091247534</v>
+        <v>0.01671303745747379</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -469,10 +469,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.03093650709530273</v>
+        <v>0.01630795964005197</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03093650709530273</v>
+        <v>0.01630795964005197</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -483,10 +483,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03027513545465629</v>
+        <v>0.01593064246921595</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03027513545465629</v>
+        <v>0.01593064246921595</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -497,10 +497,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.03029394239700569</v>
+        <v>0.01595993901410477</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03029394239700569</v>
+        <v>0.01595993901410477</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -511,10 +511,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.03172927010207313</v>
+        <v>0.01679044498225423</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03172927010207313</v>
+        <v>0.01679044498225423</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -525,10 +525,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.03508370043399022</v>
+        <v>0.01868532679564873</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03508370043399022</v>
+        <v>0.01868532679564873</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -539,10 +539,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.04090315100798075</v>
+        <v>0.02192743862045417</v>
       </c>
       <c r="C8" t="n">
-        <v>0.04090315100798075</v>
+        <v>0.02192743862045417</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -553,10 +553,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.04920089409971645</v>
+        <v>0.02650609795041597</v>
       </c>
       <c r="C9" t="n">
-        <v>0.04920089409971645</v>
+        <v>0.02650609795041597</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -567,10 +567,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.05928986108275713</v>
+        <v>0.03202167240899289</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05928986108275713</v>
+        <v>0.03202167240899289</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -581,10 +581,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.07041597472211551</v>
+        <v>0.0380336271617728</v>
       </c>
       <c r="C11" t="n">
-        <v>0.07041597472211551</v>
+        <v>0.0380336271617728</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -595,10 +595,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.08178897973023588</v>
+        <v>0.04410294406152356</v>
       </c>
       <c r="C12" t="n">
-        <v>0.08178897973023588</v>
+        <v>0.04410294406152356</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -609,10 +609,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0931406107240222</v>
+        <v>0.05010857518112916</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0931406107240222</v>
+        <v>0.05010857518112916</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -623,10 +623,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1058265825727742</v>
+        <v>0.05683716043158359</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1058265825727742</v>
+        <v>0.05683716043158359</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -637,10 +637,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.1202597702244211</v>
+        <v>0.06455016269729588</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1202597702244211</v>
+        <v>0.06455016269729588</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -651,10 +651,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.1358518213649554</v>
+        <v>0.07294692611924514</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1358518213649554</v>
+        <v>0.07294692611924514</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -665,10 +665,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.1514427913893466</v>
+        <v>0.0813828522105339</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1514427913893466</v>
+        <v>0.0813828522105339</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -679,10 +679,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.1654366383776239</v>
+        <v>0.08897884810524088</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1654366383776239</v>
+        <v>0.08897884810524088</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.1784133963143879</v>
+        <v>0.09602104354394418</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1784133963143879</v>
+        <v>0.09602104354394418</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -707,10 +707,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.1891866398065944</v>
+        <v>0.101864012789355</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1891866398065944</v>
+        <v>0.101864012789355</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -721,10 +721,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.1974371611587867</v>
+        <v>0.1063249308326924</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1974371611587867</v>
+        <v>0.1063249308326924</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -735,10 +735,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.2030915529134244</v>
+        <v>0.1093550444764771</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2030915529134244</v>
+        <v>0.1093550444764771</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -749,10 +749,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.2067217521206769</v>
+        <v>0.111289900087799</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2067217521206769</v>
+        <v>0.111289900087799</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -763,10 +763,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.2096717756405584</v>
+        <v>0.1128385658248598</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2096717756405584</v>
+        <v>0.1128385658248598</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -777,10 +777,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.2100618787478972</v>
+        <v>0.1130175088456303</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2100618787478972</v>
+        <v>0.1130175088456303</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -791,10 +791,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.2091175989828684</v>
+        <v>0.1124899020031751</v>
       </c>
       <c r="C26" t="n">
-        <v>0.2091175989828684</v>
+        <v>0.1124899020031751</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -805,10 +805,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.2072392060112612</v>
+        <v>0.1114594604322534</v>
       </c>
       <c r="C27" t="n">
-        <v>0.2072392060112612</v>
+        <v>0.1114594604322534</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -819,10 +819,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.203990601924802</v>
+        <v>0.1097639828945469</v>
       </c>
       <c r="C28" t="n">
-        <v>0.203990601924802</v>
+        <v>0.1097639828945469</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -833,10 +833,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.2018716922089396</v>
+        <v>0.1086684795025271</v>
       </c>
       <c r="C29" t="n">
-        <v>0.2018716922089396</v>
+        <v>0.1086684795025271</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -847,10 +847,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.1961234875598803</v>
+        <v>0.105490688417674</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1961234875598803</v>
+        <v>0.105490688417674</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -861,10 +861,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.192276221936271</v>
+        <v>0.1034717221531948</v>
       </c>
       <c r="C31" t="n">
-        <v>0.192276221936271</v>
+        <v>0.1034717221531948</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
